--- a/Excel/MonsterMythConfig.xlsx
+++ b/Excel/MonsterMythConfig.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="331">
   <si>
     <t>#</t>
   </si>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>神界统领</t>
+  </si>
+  <si>
+    <t>Miss</t>
   </si>
   <si>
     <t>魔域小鸡</t>
@@ -17561,24 +17564,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="16.25" customWidth="1"/>
     <col min="8" max="8" width="17.4166666666667" customWidth="1"/>
     <col min="9" max="9" width="15.75" customWidth="1"/>
-    <col min="10" max="10" width="11.1666666666667" customWidth="1"/>
-    <col min="11" max="11" width="12.5" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="12.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="15.9166666666667" customWidth="1"/>
-    <col min="15" max="15" width="11.4166666666667" customWidth="1"/>
-    <col min="16" max="16" width="12.9166666666667" customWidth="1"/>
-    <col min="18" max="18" width="16.4166666666667" customWidth="1"/>
+    <col min="10" max="11" width="11.1666666666667" customWidth="1"/>
+    <col min="12" max="12" width="12.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="12.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="15.9166666666667" customWidth="1"/>
+    <col min="16" max="16" width="11.4166666666667" customWidth="1"/>
+    <col min="17" max="17" width="12.9166666666667" customWidth="1"/>
+    <col min="19" max="19" width="16.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
@@ -17587,7 +17590,7 @@
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
-      <c r="K1" s="4"/>
+      <c r="K1" s="6"/>
       <c r="L1" s="4"/>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
@@ -17595,9 +17598,7 @@
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
-      <c r="S1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="S1" s="4"/>
       <c r="T1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17607,8 +17608,11 @@
       <c r="V1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="W1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
@@ -17617,7 +17621,7 @@
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
-      <c r="K2" s="4"/>
+      <c r="K2" s="6"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
@@ -17625,9 +17629,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
-      <c r="S2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="S2" s="4"/>
       <c r="T2" s="1" t="s">
         <v>0</v>
       </c>
@@ -17637,8 +17639,11 @@
       <c r="V2" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:22">
+      <c r="W2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="7" t="s">
@@ -17665,32 +17670,35 @@
       <c r="J3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="L3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="M3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="N3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="O3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="7" t="s">
@@ -17717,32 +17725,35 @@
       <c r="J4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="M4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="N4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="S4" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="7" t="s">
@@ -17769,7 +17780,7 @@
       <c r="J5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -17788,13 +17799,16 @@
         <v>18</v>
       </c>
       <c r="Q5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R5" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="S5" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C6" s="5">
         <v>241</v>
       </c>
@@ -17805,26 +17819,26 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>139</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J6" s="10">
         <v>360</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="10">
+        <v>5</v>
+      </c>
+      <c r="L6" s="2">
         <v>100</v>
       </c>
-      <c r="L6" s="2">
-        <v>1800</v>
-      </c>
       <c r="M6" s="2">
         <v>1800</v>
       </c>
@@ -17832,31 +17846,34 @@
         <v>1800</v>
       </c>
       <c r="O6" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P6" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R6" s="16" t="s">
+      <c r="S6" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="S6" s="2">
-        <v>1</v>
-      </c>
       <c r="T6" s="2">
         <v>1</v>
       </c>
       <c r="U6" s="2">
         <v>1</v>
       </c>
-      <c r="V6" s="16" t="s">
+      <c r="V6" s="2">
+        <v>1</v>
+      </c>
+      <c r="W6" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C7" s="5">
         <v>242</v>
       </c>
@@ -17867,10 +17884,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G7" s="10">
-        <f t="shared" ref="G7:I7" si="0">G6*S7</f>
+        <f t="shared" ref="G7:I7" si="0">G6*T7</f>
         <v>3740000000</v>
       </c>
       <c r="H7" s="10">
@@ -17885,12 +17902,13 @@
         <f t="shared" ref="J7:J10" si="1">J6+10</f>
         <v>370</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="10">
+        <f t="shared" ref="K7:K10" si="2">K6+5</f>
+        <v>10</v>
+      </c>
+      <c r="L7" s="2">
         <v>100</v>
       </c>
-      <c r="L7" s="2">
-        <v>1800</v>
-      </c>
       <c r="M7" s="2">
         <v>1800</v>
       </c>
@@ -17898,31 +17916,34 @@
         <v>1800</v>
       </c>
       <c r="O7" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P7" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>0</v>
+      </c>
+      <c r="R7" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="R7" s="16" t="s">
+      <c r="S7" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S7" s="2">
-        <v>1.1</v>
       </c>
       <c r="T7" s="2">
         <v>1.1</v>
       </c>
       <c r="U7" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="V7" s="2">
         <v>1.2</v>
       </c>
-      <c r="V7" s="16" t="s">
+      <c r="W7" s="16" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C8" s="5">
         <v>243</v>
       </c>
@@ -17933,30 +17954,31 @@
         <v>3</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G8" s="10">
-        <f t="shared" ref="G8:I8" si="2">G6*S8</f>
+        <f t="shared" ref="G8:I8" si="3">G6*T8</f>
         <v>3910000000</v>
       </c>
       <c r="H8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2760000000</v>
       </c>
       <c r="I8" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>750000000000000</v>
       </c>
       <c r="J8" s="10">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="10">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
         <v>100</v>
       </c>
-      <c r="L8" s="2">
-        <v>1800</v>
-      </c>
       <c r="M8" s="2">
         <v>1800</v>
       </c>
@@ -17964,31 +17986,34 @@
         <v>1800</v>
       </c>
       <c r="O8" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P8" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R8" s="16" t="s">
+      <c r="S8" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S8" s="2">
-        <v>1.15</v>
       </c>
       <c r="T8" s="2">
         <v>1.15</v>
       </c>
       <c r="U8" s="2">
+        <v>1.15</v>
+      </c>
+      <c r="V8" s="2">
         <v>1.5</v>
       </c>
-      <c r="V8" s="16" t="s">
+      <c r="W8" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C9" s="5">
         <v>244</v>
       </c>
@@ -17999,30 +18024,31 @@
         <v>4</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G9" s="10">
-        <f t="shared" ref="G9:I9" si="3">G6*S9</f>
+        <f t="shared" ref="G9:I9" si="4">G6*T9</f>
         <v>4080000000</v>
       </c>
       <c r="H9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2880000000</v>
       </c>
       <c r="I9" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>900000000000000</v>
       </c>
       <c r="J9" s="10">
         <f t="shared" si="1"/>
         <v>390</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="10">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="L9" s="2">
         <v>100</v>
       </c>
-      <c r="L9" s="2">
-        <v>1800</v>
-      </c>
       <c r="M9" s="2">
         <v>1800</v>
       </c>
@@ -18030,31 +18056,34 @@
         <v>1800</v>
       </c>
       <c r="O9" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="R9" s="16" t="s">
+      <c r="S9" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="S9" s="2">
-        <v>1.2</v>
       </c>
       <c r="T9" s="2">
         <v>1.2</v>
       </c>
       <c r="U9" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="V9" s="2">
         <v>1.8</v>
       </c>
-      <c r="V9" s="16" t="s">
+      <c r="W9" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:22">
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:23">
       <c r="C10" s="5">
         <v>245</v>
       </c>
@@ -18065,30 +18094,31 @@
         <v>5</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G10" s="12">
-        <f t="shared" ref="G10:I10" si="4">G6*S10</f>
+        <f t="shared" ref="G10:I10" si="5">G6*T10</f>
         <v>4250000000</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3000000000</v>
       </c>
       <c r="I10" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1250000000000000</v>
       </c>
       <c r="J10" s="12">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="10">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
-        <v>1800</v>
-      </c>
       <c r="M10" s="3">
         <v>1800</v>
       </c>
@@ -18096,34 +18126,37 @@
         <v>1800</v>
       </c>
       <c r="O10" s="3">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P10" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
+      </c>
+      <c r="R10" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="R10" s="18" t="s">
+      <c r="S10" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1.25</v>
       </c>
       <c r="T10" s="3">
         <v>1.25</v>
       </c>
       <c r="U10" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="V10" s="3">
         <v>2.5</v>
       </c>
-      <c r="V10" s="18" t="s">
+      <c r="W10" s="18" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="F11" s="5"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C12" s="5">
         <v>246</v>
       </c>
@@ -18134,26 +18167,26 @@
         <v>1</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J12" s="10">
         <v>360</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="10">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
         <v>100</v>
       </c>
-      <c r="L12" s="2">
-        <v>1800</v>
-      </c>
       <c r="M12" s="2">
         <v>1800</v>
       </c>
@@ -18161,31 +18194,34 @@
         <v>1800</v>
       </c>
       <c r="O12" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P12" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R12" s="16" t="s">
+      <c r="S12" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="S12" s="2">
-        <v>1</v>
-      </c>
       <c r="T12" s="2">
         <v>1</v>
       </c>
       <c r="U12" s="2">
         <v>1</v>
       </c>
-      <c r="V12" s="16" t="s">
+      <c r="V12" s="2">
+        <v>1</v>
+      </c>
+      <c r="W12" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C13" s="5">
         <v>247</v>
       </c>
@@ -18196,30 +18232,31 @@
         <v>2</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G13" s="10">
-        <f t="shared" ref="G13:I13" si="5">G12*S13</f>
+        <f t="shared" ref="G13:I13" si="6">G12*T13</f>
         <v>4620000000</v>
       </c>
       <c r="H13" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3960000000</v>
       </c>
       <c r="I13" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>960000000000000</v>
       </c>
       <c r="J13" s="10">
-        <f t="shared" ref="J13:J16" si="6">J12+10</f>
+        <f t="shared" ref="J13:J16" si="7">J12+10</f>
         <v>370</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="10">
+        <f t="shared" ref="K13:K16" si="8">K12+5</f>
+        <v>20</v>
+      </c>
+      <c r="L13" s="2">
         <v>100</v>
       </c>
-      <c r="L13" s="2">
-        <v>1800</v>
-      </c>
       <c r="M13" s="2">
         <v>1800</v>
       </c>
@@ -18227,31 +18264,34 @@
         <v>1800</v>
       </c>
       <c r="O13" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P13" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="R13" s="16" t="s">
+      <c r="S13" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S13" s="2">
-        <v>1.1</v>
       </c>
       <c r="T13" s="2">
         <v>1.1</v>
       </c>
       <c r="U13" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="V13" s="2">
         <v>1.2</v>
       </c>
-      <c r="V13" s="16" t="s">
+      <c r="W13" s="16" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C14" s="5">
         <v>248</v>
       </c>
@@ -18262,30 +18302,31 @@
         <v>3</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G14" s="10">
-        <f t="shared" ref="G14:I14" si="7">G12*S14</f>
+        <f t="shared" ref="G14:I14" si="9">G12*T14</f>
         <v>4830000000</v>
       </c>
       <c r="H14" s="10">
+        <f t="shared" si="9"/>
+        <v>4140000000</v>
+      </c>
+      <c r="I14" s="10">
+        <f t="shared" si="9"/>
+        <v>1200000000000000</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="7"/>
-        <v>4140000000</v>
-      </c>
-      <c r="I14" s="10">
-        <f t="shared" si="7"/>
-        <v>1200000000000000</v>
-      </c>
-      <c r="J14" s="10">
-        <f t="shared" si="6"/>
         <v>380</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="10">
+        <f t="shared" si="8"/>
+        <v>25</v>
+      </c>
+      <c r="L14" s="2">
         <v>100</v>
       </c>
-      <c r="L14" s="2">
-        <v>1800</v>
-      </c>
       <c r="M14" s="2">
         <v>1800</v>
       </c>
@@ -18293,31 +18334,34 @@
         <v>1800</v>
       </c>
       <c r="O14" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P14" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>0</v>
+      </c>
+      <c r="R14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R14" s="16" t="s">
+      <c r="S14" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S14" s="2">
-        <v>1.15</v>
       </c>
       <c r="T14" s="2">
         <v>1.15</v>
       </c>
       <c r="U14" s="2">
+        <v>1.15</v>
+      </c>
+      <c r="V14" s="2">
         <v>1.5</v>
       </c>
-      <c r="V14" s="16" t="s">
+      <c r="W14" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:22">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:23">
       <c r="C15" s="5">
         <v>249</v>
       </c>
@@ -18328,30 +18372,31 @@
         <v>4</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G15" s="10">
-        <f t="shared" ref="G15:I15" si="8">G12*S15</f>
+        <f t="shared" ref="G15:I15" si="10">G12*T15</f>
         <v>5040000000</v>
       </c>
       <c r="H15" s="10">
+        <f t="shared" si="10"/>
+        <v>4320000000</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="10"/>
+        <v>1440000000000000</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="7"/>
+        <v>390</v>
+      </c>
+      <c r="K15" s="10">
         <f t="shared" si="8"/>
-        <v>4320000000</v>
-      </c>
-      <c r="I15" s="10">
-        <f t="shared" si="8"/>
-        <v>1440000000000000</v>
-      </c>
-      <c r="J15" s="10">
-        <f t="shared" si="6"/>
-        <v>390</v>
-      </c>
-      <c r="K15" s="2">
+        <v>30</v>
+      </c>
+      <c r="L15" s="2">
         <v>100</v>
       </c>
-      <c r="L15" s="2">
-        <v>1800</v>
-      </c>
       <c r="M15" s="2">
         <v>1800</v>
       </c>
@@ -18359,31 +18404,34 @@
         <v>1800</v>
       </c>
       <c r="O15" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P15" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
+      <c r="R15" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="R15" s="16" t="s">
+      <c r="S15" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="S15" s="2">
-        <v>1.2</v>
       </c>
       <c r="T15" s="2">
         <v>1.2</v>
       </c>
       <c r="U15" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="V15" s="2">
         <v>1.8</v>
       </c>
-      <c r="V15" s="16" t="s">
+      <c r="W15" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:22">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:23">
       <c r="C16" s="5">
         <v>250</v>
       </c>
@@ -18394,30 +18442,31 @@
         <v>5</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="12">
-        <f t="shared" ref="G16:I16" si="9">G12*S16</f>
+        <f t="shared" ref="G16:I16" si="11">G12*T16</f>
         <v>5250000000</v>
       </c>
       <c r="H16" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>4500000000</v>
       </c>
       <c r="I16" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>2000000000000000</v>
       </c>
       <c r="J16" s="12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>400</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="10">
+        <f t="shared" si="8"/>
+        <v>35</v>
+      </c>
+      <c r="L16" s="3">
         <v>100</v>
       </c>
-      <c r="L16" s="3">
-        <v>1800</v>
-      </c>
       <c r="M16" s="3">
         <v>1800</v>
       </c>
@@ -18425,34 +18474,37 @@
         <v>1800</v>
       </c>
       <c r="O16" s="3">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P16" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>0</v>
+      </c>
+      <c r="R16" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="R16" s="18" t="s">
+      <c r="S16" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="S16" s="3">
-        <v>1.25</v>
       </c>
       <c r="T16" s="3">
         <v>1.25</v>
       </c>
       <c r="U16" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="V16" s="3">
         <v>2.5</v>
       </c>
-      <c r="V16" s="18" t="s">
+      <c r="W16" s="18" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="3:22">
+    <row r="17" spans="3:23">
       <c r="F17" s="5"/>
     </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:22">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C18" s="5">
         <v>251</v>
       </c>
@@ -18463,26 +18515,26 @@
         <v>1</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>155</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J18" s="10">
         <v>360</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="10">
+        <v>30</v>
+      </c>
+      <c r="L18" s="2">
         <v>100</v>
       </c>
-      <c r="L18" s="2">
-        <v>1800</v>
-      </c>
       <c r="M18" s="2">
         <v>1800</v>
       </c>
@@ -18490,31 +18542,34 @@
         <v>1800</v>
       </c>
       <c r="O18" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P18" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>0</v>
+      </c>
+      <c r="R18" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R18" s="16" t="s">
+      <c r="S18" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="S18" s="2">
-        <v>1</v>
-      </c>
       <c r="T18" s="2">
         <v>1</v>
       </c>
       <c r="U18" s="2">
         <v>1</v>
       </c>
-      <c r="V18" s="16" t="s">
+      <c r="V18" s="2">
+        <v>1</v>
+      </c>
+      <c r="W18" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:22">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C19" s="5">
         <v>252</v>
       </c>
@@ -18525,30 +18580,31 @@
         <v>2</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" ref="G19:I19" si="10">G18*S19</f>
+        <f t="shared" ref="G19:I19" si="12">G18*T19</f>
         <v>5610000000</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>6600000000</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1440000000000000</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" ref="J19:J22" si="11">J18+10</f>
+        <f t="shared" ref="J19:J22" si="13">J18+10</f>
         <v>370</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="10">
+        <f t="shared" ref="K19:K22" si="14">K18+5</f>
+        <v>35</v>
+      </c>
+      <c r="L19" s="2">
         <v>100</v>
       </c>
-      <c r="L19" s="2">
-        <v>1800</v>
-      </c>
       <c r="M19" s="2">
         <v>1800</v>
       </c>
@@ -18556,31 +18612,34 @@
         <v>1800</v>
       </c>
       <c r="O19" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P19" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>0</v>
+      </c>
+      <c r="R19" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="R19" s="16" t="s">
+      <c r="S19" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S19" s="2">
-        <v>1.1</v>
       </c>
       <c r="T19" s="2">
         <v>1.1</v>
       </c>
       <c r="U19" s="2">
+        <v>1.1</v>
+      </c>
+      <c r="V19" s="2">
         <v>1.2</v>
       </c>
-      <c r="V19" s="16" t="s">
+      <c r="W19" s="16" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:22">
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C20" s="5">
         <v>253</v>
       </c>
@@ -18591,30 +18650,31 @@
         <v>3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:I20" si="12">G18*S20</f>
+        <f t="shared" ref="G20:I20" si="15">G18*T20</f>
         <v>5865000000</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>6900000000</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1800000000000000</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>380</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="10">
+        <f t="shared" si="14"/>
+        <v>40</v>
+      </c>
+      <c r="L20" s="2">
         <v>100</v>
       </c>
-      <c r="L20" s="2">
-        <v>1800</v>
-      </c>
       <c r="M20" s="2">
         <v>1800</v>
       </c>
@@ -18622,31 +18682,34 @@
         <v>1800</v>
       </c>
       <c r="O20" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P20" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="R20" s="16" t="s">
+      <c r="S20" s="16" t="s">
         <v>183</v>
-      </c>
-      <c r="S20" s="2">
-        <v>1.15</v>
       </c>
       <c r="T20" s="2">
         <v>1.15</v>
       </c>
       <c r="U20" s="2">
+        <v>1.15</v>
+      </c>
+      <c r="V20" s="2">
         <v>1.5</v>
       </c>
-      <c r="V20" s="16" t="s">
+      <c r="W20" s="16" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:22">
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C21" s="5">
         <v>254</v>
       </c>
@@ -18657,30 +18720,31 @@
         <v>4</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" ref="G21:I21" si="13">G18*S21</f>
+        <f t="shared" ref="G21:I21" si="16">G18*T21</f>
         <v>6120000000</v>
       </c>
       <c r="H21" s="10">
+        <f t="shared" si="16"/>
+        <v>7200000000</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="16"/>
+        <v>2160000000000000</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="13"/>
-        <v>7200000000</v>
-      </c>
-      <c r="I21" s="10">
-        <f t="shared" si="13"/>
-        <v>2160000000000000</v>
-      </c>
-      <c r="J21" s="10">
-        <f t="shared" si="11"/>
         <v>390</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="10">
+        <f t="shared" si="14"/>
+        <v>45</v>
+      </c>
+      <c r="L21" s="2">
         <v>100</v>
       </c>
-      <c r="L21" s="2">
-        <v>1800</v>
-      </c>
       <c r="M21" s="2">
         <v>1800</v>
       </c>
@@ -18688,31 +18752,34 @@
         <v>1800</v>
       </c>
       <c r="O21" s="2">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P21" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0</v>
+      </c>
+      <c r="R21" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="R21" s="16" t="s">
+      <c r="S21" s="16" t="s">
         <v>189</v>
-      </c>
-      <c r="S21" s="2">
-        <v>1.2</v>
       </c>
       <c r="T21" s="2">
         <v>1.2</v>
       </c>
       <c r="U21" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="V21" s="2">
         <v>1.8</v>
       </c>
-      <c r="V21" s="16" t="s">
+      <c r="W21" s="16" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="3:22">
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="3:23">
       <c r="C22" s="5">
         <v>255</v>
       </c>
@@ -18723,30 +18790,31 @@
         <v>5</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G22" s="12">
-        <f t="shared" ref="G22:I22" si="14">G18*S22</f>
+        <f t="shared" ref="G22:I22" si="17">G18*T22</f>
         <v>6375000000</v>
       </c>
       <c r="H22" s="12">
+        <f t="shared" si="17"/>
+        <v>7500000000</v>
+      </c>
+      <c r="I22" s="12">
+        <f t="shared" si="17"/>
+        <v>3000000000000000</v>
+      </c>
+      <c r="J22" s="12">
+        <f t="shared" si="13"/>
+        <v>400</v>
+      </c>
+      <c r="K22" s="10">
         <f t="shared" si="14"/>
-        <v>7500000000</v>
-      </c>
-      <c r="I22" s="12">
-        <f t="shared" si="14"/>
-        <v>3000000000000000</v>
-      </c>
-      <c r="J22" s="12">
-        <f t="shared" si="11"/>
-        <v>400</v>
-      </c>
-      <c r="K22" s="3">
+        <v>50</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>1800</v>
-      </c>
       <c r="M22" s="3">
         <v>1800</v>
       </c>
@@ -18754,36 +18822,39 @@
         <v>1800</v>
       </c>
       <c r="O22" s="3">
-        <v>99</v>
+        <v>1800</v>
       </c>
       <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="R22" s="18" t="s">
+      <c r="S22" s="18" t="s">
         <v>189</v>
-      </c>
-      <c r="S22" s="3">
-        <v>1.25</v>
       </c>
       <c r="T22" s="3">
         <v>1.25</v>
       </c>
       <c r="U22" s="3">
+        <v>1.25</v>
+      </c>
+      <c r="V22" s="3">
         <v>2.5</v>
       </c>
-      <c r="V22" s="18" t="s">
+      <c r="W22" s="18" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="3:22">
+    <row r="23" spans="3:23">
       <c r="F23" s="13"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:R5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:S5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
